--- a/Data/t17.1.xlsx
+++ b/Data/t17.1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="3">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73.40000000000001</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="4">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="15">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>87.3</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="19">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>74.8</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="27">
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>75.09999999999999</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="28">
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="29">
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="35">
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="36">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="37">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>72.59999999999999</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="41">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="42">
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="43">
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>77.5</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="44">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="47">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>87</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>73.90000000000001</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="49">
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="50">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="51">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>78</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="52">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="53">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>81.3</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="55">
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>86.40000000000001</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="56">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>74.09999999999999</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57">
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1873,17 +1873,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>31.4</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>68.59999999999999</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1923,17 +1923,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>17.6</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1948,17 +1948,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>82.40000000000001</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1973,17 +1973,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>11.1</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1998,17 +1998,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>88.90000000000001</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2023,17 +2023,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>66.2</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2048,11 +2048,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>33.8</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="66">
@@ -2073,11 +2073,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>30.5</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="67">
@@ -2098,11 +2098,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>69.5</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="68">
@@ -2123,11 +2123,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="69">
@@ -2148,11 +2148,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>82.8</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="70">
@@ -2173,11 +2173,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="71">
@@ -2198,11 +2198,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>90</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -2223,11 +2223,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>67.40000000000001</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="73">
@@ -2248,11 +2248,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>32.6</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="74">
@@ -2273,11 +2273,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>31.4</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="75">
@@ -2298,11 +2298,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>68.59999999999999</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="76">
@@ -2323,11 +2323,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>18.8</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="77">
@@ -2348,11 +2348,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>81.2</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="78">
@@ -2373,11 +2373,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79">
@@ -2398,11 +2398,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>89.59999999999999</v>
+        <v>90</v>
       </c>
     </row>
     <row r="80">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>67.09999999999999</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -2448,11 +2448,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>32.9</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="82">
@@ -2473,11 +2473,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>30.3</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="83">
@@ -2498,11 +2498,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>69.7</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="84">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2573,11 +2573,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>9</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="87">
@@ -2598,11 +2598,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>91</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="88">
@@ -2623,11 +2623,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>65.3</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="89">
@@ -2648,11 +2648,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>34.7</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="90">
@@ -2673,11 +2673,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>27.4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91">
@@ -2698,11 +2698,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>72.59999999999999</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92">
@@ -2723,11 +2723,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>17.6</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="93">
@@ -2748,11 +2748,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>82.40000000000001</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="94">
@@ -2773,11 +2773,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
@@ -2798,11 +2798,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>90.09999999999999</v>
+        <v>91</v>
       </c>
     </row>
     <row r="96">
@@ -2823,11 +2823,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>63.2</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="97">
@@ -2848,11 +2848,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>36.8</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="98">
@@ -2873,11 +2873,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>26.1</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="99">
@@ -2898,11 +2898,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>73.90000000000001</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="100">
@@ -2923,11 +2923,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>18.1</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="101">
@@ -2948,11 +2948,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>81.90000000000001</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="102">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -3023,11 +3023,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>64.7</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="105">
@@ -3048,11 +3048,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>35.3</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="106">
@@ -3073,11 +3073,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="107">
@@ -3098,11 +3098,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="108">
@@ -3123,11 +3123,11 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>18.7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109">
@@ -3148,11 +3148,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>81.3</v>
+        <v>82</v>
       </c>
     </row>
     <row r="110">
@@ -3173,11 +3173,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -3198,11 +3198,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>90.5</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="112">
@@ -3223,11 +3223,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>63.6</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="113">
@@ -3248,17 +3248,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>36.4</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3273,17 +3273,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>39.1</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3298,17 +3298,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>60.9</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3323,17 +3323,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>22.8</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3348,17 +3348,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>77.2</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3373,17 +3373,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>17.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>82.5</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3423,17 +3423,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>68.2</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3448,17 +3448,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>31.8</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3473,17 +3473,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>38.8</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3498,17 +3498,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>61.2</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>21.4</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3548,17 +3548,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>78.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>25.3</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3598,17 +3598,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>74.7</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3623,17 +3623,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>61.3</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3648,11 +3648,11 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>38.7</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="130">
@@ -3673,11 +3673,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="131">
@@ -3698,11 +3698,11 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="132">
@@ -3723,11 +3723,11 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>21.4</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="133">
@@ -3748,11 +3748,11 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>78.59999999999999</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="134">
@@ -3773,11 +3773,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="135">
@@ -3798,11 +3798,11 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>83.5</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="136">
@@ -3823,11 +3823,11 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>63.9</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="137">
@@ -3848,11 +3848,11 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>36.1</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="138">
@@ -3873,11 +3873,11 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>39.7</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="139">
@@ -3898,11 +3898,11 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>60.3</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="140">
@@ -3923,11 +3923,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>23</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="141">
@@ -3948,11 +3948,11 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>77</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="142">
@@ -3973,11 +3973,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>14.4</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="143">
@@ -3998,11 +3998,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>85.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="144">
@@ -4023,11 +4023,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>66.09999999999999</v>
+        <v>61</v>
       </c>
     </row>
     <row r="145">
@@ -4048,11 +4048,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>33.9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="146">
@@ -4073,11 +4073,11 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>37.9</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="147">
@@ -4098,11 +4098,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>62.1</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="148">
@@ -4123,11 +4123,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>24.6</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="149">
@@ -4148,11 +4148,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>75.40000000000001</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="150">
@@ -4173,11 +4173,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>9.1</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="151">
@@ -4198,11 +4198,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>90.90000000000001</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="152">
@@ -4223,11 +4223,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>66.59999999999999</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="153">
@@ -4248,11 +4248,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>33.4</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="154">
@@ -4273,11 +4273,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>32.7</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="155">
@@ -4298,11 +4298,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>67.3</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="156">
@@ -4323,11 +4323,11 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>20.5</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="157">
@@ -4348,11 +4348,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>79.5</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="158">
@@ -4373,11 +4373,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>16.4</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="159">
@@ -4398,11 +4398,11 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>83.59999999999999</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="160">
@@ -4423,11 +4423,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>68.2</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -4448,11 +4448,11 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>31.8</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="162">
@@ -4473,11 +4473,11 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>29.6</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="163">
@@ -4498,11 +4498,11 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>70.40000000000001</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="164">
@@ -4523,11 +4523,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>25</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="165">
@@ -4548,11 +4548,11 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="166">
@@ -4573,11 +4573,11 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>10.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="167">
@@ -4598,11 +4598,11 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>89.40000000000001</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="168">
@@ -4623,11 +4623,11 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>64.8</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="169">
@@ -4648,11 +4648,611 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>33.7</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Creche e pré-escola</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Creche e pré-escola</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>67.8</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Ensino Fundamental</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Ensino Fundamental</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>79.59999999999999</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Ensino Médio</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Ensino Médio</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>83.90000000000001</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Superior - Graduação</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>68.09999999999999</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Superior - Graduação</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Creche e pré-escola</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
           <t>01/01/2024</t>
         </is>
       </c>
-      <c r="E169" t="n">
+      <c r="E178" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Creche e pré-escola</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>70.90000000000001</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Ensino Fundamental</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Ensino Fundamental</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>74.90000000000001</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Ensino Médio</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Ensino Médio</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>89.59999999999999</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Superior - Graduação</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Superior - Graduação</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
         <v>35.2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Creche e pré-escola</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Creche e pré-escola</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>68.59999999999999</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Ensino Fundamental</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Ensino Fundamental</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>75.59999999999999</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Ensino Médio</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Ensino Médio</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Superior - Graduação</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Superior - Graduação</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>31.5</v>
       </c>
     </row>
   </sheetData>
